--- a/artfynd/A 26277-2024 artfynd.xlsx
+++ b/artfynd/A 26277-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119785609</v>
+        <v>119785519</v>
       </c>
       <c r="B2" t="n">
-        <v>97929</v>
+        <v>110037</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västerängshalsen, Västerängshalsen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690871</v>
+        <v>690863</v>
       </c>
       <c r="R2" t="n">
-        <v>6684766</v>
+        <v>6684754</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119785519</v>
+        <v>119785609</v>
       </c>
       <c r="B3" t="n">
-        <v>110037</v>
+        <v>97929</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,34 +803,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västerängshalsen, Västerängshalsen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690863</v>
+        <v>690871</v>
       </c>
       <c r="R3" t="n">
-        <v>6684754</v>
+        <v>6684766</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 26277-2024 artfynd.xlsx
+++ b/artfynd/A 26277-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119785519</v>
       </c>
       <c r="B2" t="n">
-        <v>110037</v>
+        <v>110061</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>119785609</v>
       </c>
       <c r="B3" t="n">
-        <v>97929</v>
+        <v>97952</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 26277-2024 artfynd.xlsx
+++ b/artfynd/A 26277-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119785519</v>
+        <v>119785609</v>
       </c>
       <c r="B2" t="n">
-        <v>110061</v>
+        <v>97952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västerängshalsen, Västerängshalsen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690863</v>
+        <v>690871</v>
       </c>
       <c r="R2" t="n">
-        <v>6684754</v>
+        <v>6684766</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119785609</v>
+        <v>119785519</v>
       </c>
       <c r="B3" t="n">
-        <v>97952</v>
+        <v>110061</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,43 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>219711</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västerängshalsen, Västerängshalsen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690871</v>
+        <v>690863</v>
       </c>
       <c r="R3" t="n">
-        <v>6684766</v>
+        <v>6684754</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 26277-2024 artfynd.xlsx
+++ b/artfynd/A 26277-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119785609</v>
+        <v>119788388</v>
       </c>
       <c r="B2" t="n">
-        <v>97952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västerängshalsen, Västerängshalsen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690871</v>
+        <v>690683</v>
       </c>
       <c r="R2" t="n">
-        <v>6684766</v>
+        <v>6684799</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,16 +785,11 @@
         <v>119785519</v>
       </c>
       <c r="B3" t="n">
-        <v>110061</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -905,6 +886,341 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>119785609</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västerängshalsen, Västerängshalsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>690871</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6684766</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119785148</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Västerängshalsen, Västerängshalsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>690669</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6684928</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119785088</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Västerängshalsen, Västerängshalsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>690669</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6684928</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
